--- a/2-multi-document-abbyy-vs-tiled3x2+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.113.xlsx
+++ b/2-multi-document-abbyy-vs-tiled3x2+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.113.xlsx
@@ -464,12 +464,12 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap - paddle</t>
+          <t>Possible duplicate lines - paddle</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap - abbyy</t>
+          <t>Possible duplicate lines - abbyy</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
@@ -847,7 +847,7 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap issue count</t>
+          <t>Possible duplicate lines issue count</t>
         </is>
       </c>
       <c r="B7" s="1" t="inlineStr">

--- a/2-multi-document-abbyy-vs-tiled3x2+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.113.xlsx
+++ b/2-multi-document-abbyy-vs-tiled3x2+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.113.xlsx
@@ -422,8 +422,8 @@
     <col width="39" customWidth="1" min="1" max="1"/>
     <col width="60" customWidth="1" min="2" max="2"/>
     <col width="60" customWidth="1" min="3" max="3"/>
-    <col width="33" customWidth="1" min="4" max="4"/>
-    <col width="32" customWidth="1" min="5" max="5"/>
+    <col width="35" customWidth="1" min="4" max="4"/>
+    <col width="34" customWidth="1" min="5" max="5"/>
     <col width="36" customWidth="1" min="6" max="6"/>
     <col width="35" customWidth="1" min="7" max="7"/>
     <col width="27" customWidth="1" min="8" max="8"/>
@@ -431,7 +431,7 @@
     <col width="60" customWidth="1" min="10" max="10"/>
     <col width="60" customWidth="1" min="11" max="11"/>
     <col width="32" customWidth="1" min="12" max="12"/>
-    <col width="31" customWidth="1" min="13" max="13"/>
+    <col width="60" customWidth="1" min="13" max="13"/>
     <col width="50" customWidth="1" min="14" max="14"/>
     <col width="60" customWidth="1" min="15" max="15"/>
     <col width="60" customWidth="1" min="16" max="16"/>
@@ -601,16 +601,20 @@
       </c>
       <c r="J2" s="1" t="inlineStr">
         <is>
-          <t>L103: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: viz.â€”.</t>
+          <t>L123: stray/suspicious non-ASCII glyph(s): U+FF1B FULLWIDTH SEMICOLON :: in vacation ； although it is generally</t>
         </is>
       </c>
       <c r="K2" s="1" t="inlineStr">
         <is>
-          <t>L38: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN :: curity forâ€¢</t>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE | symbol-only separator/garbage line :: [BOM]106</t>
         </is>
       </c>
       <c r="L2" s="1" t="inlineStr"/>
-      <c r="M2" s="1" t="inlineStr"/>
+      <c r="M2" s="1" t="inlineStr">
+        <is>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE | symbol-only separator/garbage line :: [BOM]106</t>
+        </is>
+      </c>
       <c r="N2" s="1" t="inlineStr">
         <is>
           <t>L16: symbol-only separator/garbage line :: 1850.</t>
@@ -618,7 +622,7 @@
       </c>
       <c r="O2" s="1" t="inlineStr">
         <is>
-          <t>L85: isolated marker/symbol line :: %</t>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE | symbol-only separator/garbage line :: [BOM]106</t>
         </is>
       </c>
       <c r="P2" s="1" t="inlineStr">
@@ -653,7 +657,7 @@
       </c>
       <c r="C3" s="1" t="inlineStr">
         <is>
-          <t>130</t>
+          <t>97</t>
         </is>
       </c>
       <c r="D3" s="1" t="inlineStr"/>
@@ -662,14 +666,10 @@
       <c r="G3" s="1" t="inlineStr"/>
       <c r="H3" s="1" t="inlineStr"/>
       <c r="I3" s="1" t="inlineStr"/>
-      <c r="J3" s="1" t="inlineStr">
-        <is>
-          <t>L125: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: es of a special nature â€” such as to hear</t>
-        </is>
-      </c>
+      <c r="J3" s="1" t="inlineStr"/>
       <c r="K3" s="1" t="inlineStr">
         <is>
-          <t>L57: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: viz.â€”</t>
+          <t>L38: stray/suspicious non-ASCII glyph(s): U+2022 BULLET :: curity for•</t>
         </is>
       </c>
       <c r="L3" s="1" t="inlineStr"/>
@@ -681,7 +681,7 @@
       </c>
       <c r="O3" s="1" t="inlineStr">
         <is>
-          <t>L87: symbol-only separator/garbage line :: 1850.</t>
+          <t>L85: isolated marker/symbol line :: %</t>
         </is>
       </c>
       <c r="P3" s="1" t="inlineStr"/>
@@ -720,7 +720,7 @@
       <c r="J4" s="1" t="inlineStr"/>
       <c r="K4" s="1" t="inlineStr">
         <is>
-          <t>L127: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: under circumstances of a special natureâ€”such as to hear</t>
+          <t>L130: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="L4" s="1" t="inlineStr"/>
@@ -732,7 +732,7 @@
       </c>
       <c r="O4" s="1" t="inlineStr">
         <is>
-          <t>L88: isolated marker/symbol line :: V.</t>
+          <t>L87: symbol-only separator/garbage line :: 1850.</t>
         </is>
       </c>
       <c r="P4" s="1" t="inlineStr"/>
@@ -754,12 +754,12 @@
       </c>
       <c r="B5" s="1" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="C5" s="1" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="D5" s="1" t="inlineStr"/>
@@ -769,11 +769,7 @@
       <c r="H5" s="1" t="inlineStr"/>
       <c r="I5" s="1" t="inlineStr"/>
       <c r="J5" s="1" t="inlineStr"/>
-      <c r="K5" s="1" t="inlineStr">
-        <is>
-          <t>L130: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
-        </is>
-      </c>
+      <c r="K5" s="1" t="inlineStr"/>
       <c r="L5" s="1" t="inlineStr"/>
       <c r="M5" s="1" t="inlineStr"/>
       <c r="N5" s="1" t="inlineStr">
@@ -783,7 +779,7 @@
       </c>
       <c r="O5" s="1" t="inlineStr">
         <is>
-          <t>L91: symbol-only separator/garbage line :: 1850.</t>
+          <t>L88: isolated marker/symbol line :: V.</t>
         </is>
       </c>
       <c r="P5" s="1" t="inlineStr"/>
@@ -830,7 +826,7 @@
       </c>
       <c r="O6" s="1" t="inlineStr">
         <is>
-          <t>L130: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
+          <t>L91: symbol-only separator/garbage line :: 1850.</t>
         </is>
       </c>
       <c r="P6" s="1" t="inlineStr"/>
@@ -875,7 +871,11 @@
           <t>L127: isolated marker/symbol line :: T</t>
         </is>
       </c>
-      <c r="O7" s="1" t="inlineStr"/>
+      <c r="O7" s="1" t="inlineStr">
+        <is>
+          <t>L130: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
+        </is>
+      </c>
       <c r="P7" s="1" t="inlineStr"/>
       <c r="Q7" s="1" t="inlineStr"/>
       <c r="R7" s="1" t="inlineStr"/>
@@ -973,12 +973,12 @@
       </c>
       <c r="B10" s="1" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C10" s="1" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D10" s="1" t="inlineStr"/>
@@ -1017,7 +1017,7 @@
       </c>
       <c r="C11" s="1" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D11" s="1" t="inlineStr"/>
@@ -1056,7 +1056,7 @@
       </c>
       <c r="C12" s="1" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="D12" s="1" t="inlineStr"/>
